--- a/apps/api/assets/vocabulary/初中/外研版/外研版初中英语八年级上册.xlsx
+++ b/apps/api/assets/vocabulary/初中/外研版/外研版初中英语八年级上册.xlsx
@@ -440,7 +440,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D321"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -758,6 +758,16 @@
           <t>look up</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 查找；查阅；探望；看望
@@ -793,6 +803,16 @@
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>make a mistake</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1154,6 +1174,16 @@
           <t>agree with sb.</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 适合；赞同；与…一致
@@ -1187,6 +1217,16 @@
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>ask for</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1557,6 +1597,16 @@
           <t>pretty good</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 非常好；相当好；很好</t>
@@ -1691,6 +1741,16 @@
           <t>home town</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 家乡；故乡；故园</t>
@@ -1723,6 +1783,16 @@
       <c r="A58" s="2" t="inlineStr">
         <is>
           <t>be famous for</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2087,6 +2157,16 @@
           <t>What's the matter ?</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 发生了什么事?
@@ -2264,6 +2344,16 @@
           <t>plenty of</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 很多的
@@ -2326,6 +2416,16 @@
           <t>cheer ... on</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 欢呼；喝采；高呼加油:；为某人打气
@@ -2482,6 +2582,16 @@
       <c r="A92" s="2" t="inlineStr">
         <is>
           <t>warm up</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -2850,6 +2960,16 @@
           <t>far from</t>
         </is>
       </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 远离；决不
@@ -2913,6 +3033,16 @@
           <t>all the time</t>
         </is>
       </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 始终；〔美国〕老是
@@ -3165,6 +3295,16 @@
           <t>in the end</t>
         </is>
       </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 终于
@@ -3176,6 +3316,16 @@
       <c r="A123" s="2" t="inlineStr">
         <is>
           <t>no idea</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -3329,6 +3479,16 @@
       <c r="A130" s="2" t="inlineStr">
         <is>
           <t>head teacher</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -3561,6 +3721,16 @@
           <t>in danger</t>
         </is>
       </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 在危险中
@@ -3574,6 +3744,16 @@
           <t>at last</t>
         </is>
       </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 终于
@@ -3631,6 +3811,16 @@
       <c r="A144" s="2" t="inlineStr">
         <is>
           <t>think of</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -3715,6 +3905,16 @@
       <c r="A148" s="2" t="inlineStr">
         <is>
           <t>take away</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -3778,6 +3978,16 @@
           <t>in peace</t>
         </is>
       </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 平平安安；安心
@@ -4005,6 +4215,16 @@
           <t>in order to</t>
         </is>
       </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 为了；从而；以便
@@ -4110,6 +4330,16 @@
       <c r="A166" s="2" t="inlineStr">
         <is>
           <t>nature park</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
@@ -4340,6 +4570,16 @@
           <t>tea party</t>
         </is>
       </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 茶话会；(下午) 茶会；在美国各地抗议高额税收
@@ -4373,6 +4613,16 @@
       <c r="A178" s="2" t="inlineStr">
         <is>
           <t>once or twice</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
@@ -4485,6 +4735,16 @@
       <c r="A183" s="2" t="inlineStr">
         <is>
           <t>think about</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
@@ -4749,6 +5009,16 @@
           <t>in time</t>
         </is>
       </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 经过一段时间以后；早晚；在恰好的时候；和…合拍
@@ -4762,6 +5032,16 @@
           <t>fall off ...</t>
         </is>
       </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 下降；(从马上)掉下来；扫兴颓丧；离开
@@ -4819,6 +5099,16 @@
       <c r="A198" s="2" t="inlineStr">
         <is>
           <t>pay attention</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
@@ -4860,6 +5150,16 @@
           <t>side by side</t>
         </is>
       </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 并排着
@@ -5349,6 +5649,16 @@
       <c r="A221" s="2" t="inlineStr">
         <is>
           <t>hang on</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
@@ -5462,6 +5772,16 @@
           <t>close down</t>
         </is>
       </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 关闭；关门；倒闭；歇业
@@ -6137,6 +6457,16 @@
       <c r="A255" s="2" t="inlineStr">
         <is>
           <t>come on</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
@@ -6251,6 +6581,16 @@
           <t>from time to time</t>
         </is>
       </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 时时
@@ -6338,6 +6678,16 @@
           <t>a chess set</t>
         </is>
       </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -6791,6 +7141,16 @@
           <t>for the first time</t>
         </is>
       </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 第一次
@@ -7037,6 +7397,16 @@
       <c r="A295" s="2" t="inlineStr">
         <is>
           <t>first aid</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
@@ -7124,6 +7494,16 @@
           <t>at the bottom of ...</t>
         </is>
       </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. (是)基本力量；是由于他们引起的；在…的底部
@@ -7163,6 +7543,16 @@
           <t>What's wrong with ...?</t>
         </is>
       </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 怎么了；怎么啦；有什麽不对</t>
@@ -7221,6 +7611,16 @@
       <c r="A304" s="2" t="inlineStr">
         <is>
           <t>lift up</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
@@ -7522,6 +7922,16 @@
           <t>keep clear of ...</t>
         </is>
       </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 离着
